--- a/data/trans_orig/IP31KM10_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM10_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33720</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27157</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>39871</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>62,78%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>50,56%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>74,23%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>33931</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21579</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>41443</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>63,19%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,18%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>35705</t>
+          <t>31254</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>29072</t>
+          <t>25608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42711</t>
+          <t>36337</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>55,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>69635</t>
+          <t>64975</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56258</t>
+          <t>56265</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79522</t>
+          <t>73424</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,97%</t>
+          <t>73,7%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19995</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13844</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26558</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>25,77%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>49,44%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>19768</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>12256</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>32120</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>36,81%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>22,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>59,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22640</t>
+          <t>14651</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15634</t>
+          <t>9568</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29273</t>
+          <t>20297</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>38,8%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>20,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>42408</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32521</t>
+          <t>26196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>55785</t>
+          <t>43355</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>34,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>43,52%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>360</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>282417</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>261691</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>303186</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>60,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>56,11%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>65,0%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>328</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>250192</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>227340</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>285826</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>55,37%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>50,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>63,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>360</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>297482</t>
+          <t>226879</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>273761</t>
+          <t>210144</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>320904</t>
+          <t>244236</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>547674</t>
+          <t>509296</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>514754</t>
+          <t>482721</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>587109</t>
+          <t>536768</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>57,22%</t>
+          <t>57,15%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,78%</t>
+          <t>54,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>60,24%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>184006</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>163237</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>204732</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>39,45%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>35,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>43,89%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>297</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>201640</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>166006</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>224492</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>44,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>36,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>49,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>207768</t>
+          <t>197787</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184346</t>
+          <t>180430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231489</t>
+          <t>214522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>409408</t>
+          <t>381794</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369973</t>
+          <t>354322</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442328</t>
+          <t>408369</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>42,78%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>45,83%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>80826</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69610</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>91874</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>48,49%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>41,76%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56850</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>46457</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>65974</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>38,89%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>45,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>86634</t>
+          <t>58152</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>73311</t>
+          <t>48652</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99963</t>
+          <t>69351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,19%</t>
+          <t>47,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>143483</t>
+          <t>138977</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>126779</t>
+          <t>123044</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159928</t>
+          <t>153704</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,73%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,98%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>85860</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>74812</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97076</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>51,51%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>44,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>58,24%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>89336</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>80212</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>99729</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>61,11%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>54,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>94505</t>
+          <t>88988</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81176</t>
+          <t>77789</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107828</t>
+          <t>98488</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>52,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>183841</t>
+          <t>174848</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167396</t>
+          <t>160121</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200545</t>
+          <t>190781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,71%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,14%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>60,79%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>519</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>396963</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>372106</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>422138</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>57,8%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>54,18%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>61,46%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>458</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>340973</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>314284</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>386050</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>52,32%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>48,22%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>59,24%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>519</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>419820</t>
+          <t>316285</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>394361</t>
+          <t>295711</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>449275</t>
+          <t>338404</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>760793</t>
+          <t>713249</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>723831</t>
+          <t>681789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>807651</t>
+          <t>745817</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,17%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>289861</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>264686</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>314718</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>42,2%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>38,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>45,82%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>310744</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>265667</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>337433</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>47,68%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>40,76%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>51,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>324913</t>
+          <t>301426</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>295458</t>
+          <t>279307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>350372</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>635657</t>
+          <t>591286</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>588799</t>
+          <t>558718</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672619</t>
+          <t>622746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,83%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,74%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
